--- a/Design/Excel/ET/Datas/StartConfig/StartZoneConfig.xlsx
+++ b/Design/Excel/ET/Datas/StartConfig/StartZoneConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -1101,16 +1101,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="12.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="2" customWidth="1"/>
+    <col min="2" max="3" width="12.7545454545455" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.3727272727273" style="3" customWidth="1"/>
     <col min="5" max="6" width="21" style="3" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:6">
+    <row r="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:6">
+    <row r="2" ht="16.5" customHeight="1" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:6">
+    <row r="3" ht="16.5" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" ht="16.5" customHeight="1" spans="1:6">
       <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" ht="16.5" customHeight="1" spans="1:6">
       <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="2:6">
+    <row r="6" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" ht="16.5" customHeight="1" spans="1:6">
       <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" ht="16.5" customHeight="1" spans="1:6">
       <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" ht="16.5" customHeight="1" spans="1:6">
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" ht="16.5" customHeight="1" spans="1:6">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" ht="16.5" customHeight="1" spans="1:6">
       <c r="B11" s="6" t="s">
         <v>22</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" ht="16.5" customHeight="1" spans="1:6">
       <c r="B12" s="6" t="s">
         <v>22</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" ht="16.5" customHeight="1" spans="1:6">
       <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
